--- a/04_DESIGN_TABLES/DesignTable_6901.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6901.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1171,12 +1176,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p045-t03: agrees on CHEX@HEX, C4HEX@HEX, D1@BORE; DIFFERS on D@BORE 0.45 vs Brennan A DRILL 0.460 (built to the dimension source, s6)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>6901-08-08-NWO-FG</t>
         </is>
       </c>
     </row>
@@ -2968,6 +2978,198 @@
       <c r="R45" t="inlineStr">
         <is>
           <t>6901-32-32-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6901-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6901-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3/4-16 (B UN/UNF-2A) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6901-08-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6901-08-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>6901-08-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>3/4-16 (B UN/UNF-2A) x 3/4-14 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>6901-08-12-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6901-10-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>6901-10-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>7/8-14 (B UN/UNF-2A) x 3/8-18 (A1 NPSM)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>6901-10-06-NWO-FG</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
